--- a/data_english.xlsx
+++ b/data_english.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khi_h\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khi_h\Desktop\Projets\JanaArchitect\Joud\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F301BAA5-474D-452D-8BED-F116CC97C6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B3F7F8-8049-4A4F-8423-76104D15F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{18B58FE7-2736-48EE-B9C3-1B7C87FC157D}"/>
   </bookViews>
@@ -12134,7 +12134,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>119</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>144</v>
       </c>
@@ -15314,7 +15314,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>152</v>
       </c>
@@ -17370,7 +17370,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>235</v>
       </c>
@@ -17490,7 +17490,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="242" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>240</v>
       </c>
@@ -18090,7 +18090,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>265</v>
       </c>
@@ -18572,7 +18572,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>285</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>295</v>
       </c>
@@ -19534,7 +19534,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>325</v>
       </c>
@@ -19558,7 +19558,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>326</v>
       </c>
@@ -19630,7 +19630,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="331" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>329</v>
       </c>
@@ -19798,7 +19798,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="338" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A338" s="2">
         <v>336</v>
       </c>
@@ -20734,7 +20734,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="377" spans="1:8" ht="69" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>375</v>
       </c>
@@ -21118,7 +21118,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>391</v>
       </c>
@@ -22114,7 +22114,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="435" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A435" s="2">
         <v>433</v>
       </c>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="H460" s="2"/>
     </row>
-    <row r="461" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A461" s="2">
         <v>459</v>
       </c>
@@ -24432,7 +24432,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="531" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2">
         <v>529</v>
       </c>
@@ -24480,7 +24480,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="533" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2">
         <v>531</v>
       </c>
@@ -24696,7 +24696,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="542" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A542" s="2">
         <v>540</v>
       </c>
@@ -25056,7 +25056,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="557" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2">
         <v>555</v>
       </c>
@@ -25512,7 +25512,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="576" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A576" s="2">
         <v>574</v>
       </c>
@@ -25896,7 +25896,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="592" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A592" s="2">
         <v>590</v>
       </c>
@@ -26618,7 +26618,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="622" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A622" s="2">
         <v>620</v>
       </c>
@@ -26858,7 +26858,7 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="632" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A632" s="2">
         <v>630</v>
       </c>
@@ -27964,7 +27964,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="678" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A678" s="2">
         <v>676</v>
       </c>
@@ -28204,7 +28204,7 @@
         <v>2921</v>
       </c>
     </row>
-    <row r="688" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A688" s="2">
         <v>686</v>
       </c>
@@ -28588,7 +28588,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="704" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A704" s="2">
         <v>702</v>
       </c>
@@ -29598,7 +29598,7 @@
         <v>3133</v>
       </c>
     </row>
-    <row r="746" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A746" s="2">
         <v>744</v>
       </c>
